--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T14:14:01+00:00</t>
+    <t>2026-10-06T20:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T20:02:10+00:00</t>
+    <t>2026-10-07T08:37:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T08:37:44+00:00</t>
+    <t>2026-10-07T09:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1037,7 +1037,7 @@
     <t>SubstanceAdministration.consumable</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-produit-de-sante|0.1.0}
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
   </si>
   <si>
@@ -1088,7 +1088,7 @@
     <t>SubstanceAdministration.consumable.manufacturedProduct</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-produit-de-sante|0.1.0}
 </t>
   </si>
   <si>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T09:51:04+00:00</t>
+    <t>2026-10-08T08:06:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T08:06:17+00:00</t>
+    <t>2026-10-08T10:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T10:07:19+00:00</t>
+    <t>2026-10-08T14:58:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:58:47+00:00</t>
+    <t>2026-10-12T13:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:25:25+00:00</t>
+    <t>2026-10-14T12:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
